--- a/data/file_generation/input/data_57/2025-10-19_01_00_法甲_昂热[17]VS摩纳哥[5]_标盘.xlsx
+++ b/data/file_generation/input/data_57/2025-10-19_01_00_法甲_昂热[17]VS摩纳哥[5]_标盘.xlsx
@@ -17333,26 +17333,18 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
+  <documentManagement/>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D21A9D4-D4BA-4073-8D81-C5341026CA4C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51262DC7-9933-4A6D-8ADD-AAC1F5C2D816}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{990FF3BC-53BB-435B-BC12-BDD8A3952301}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{903C05B6-9153-42BB-9AFB-53F05B862D6D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44A85C73-59C4-4565-A8AC-B92FB950D1DD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0E14284-D38E-4021-8B2F-9F3F5D564950}"/>
 </file>